--- a/Schematics in KiCad/Assembly KICad/Assembly without optional blocks/bom/T-1P21W817955A (W817955AS1P20).xlsx
+++ b/Schematics in KiCad/Assembly KICad/Assembly without optional blocks/bom/T-1P21W817955A (W817955AS1P20).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GarablueX\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GarablueX\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECAB0FF-A2DC-4F0D-9901-BE7ACF34FAF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8764AB-25E0-42BB-A06A-6203C3755B90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
   <si>
     <t>Item #</t>
   </si>
@@ -135,9 +135,6 @@
     <t>C1,C2</t>
   </si>
   <si>
-    <t>ANY</t>
-  </si>
-  <si>
     <t>10u</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t>RV1, RV2, RV3, RV4</t>
   </si>
   <si>
-    <t>any</t>
-  </si>
-  <si>
     <t>Potentiometer_Bourns_3386P_Vertical</t>
   </si>
   <si>
@@ -259,13 +253,88 @@
   </si>
   <si>
     <t>PhoenixContact_MCV_1,5_3-G-5.08_1x03_P5.08mm_Vertical</t>
+  </si>
+  <si>
+    <t>Nichicon</t>
+  </si>
+  <si>
+    <t>UFW1E100MED</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-100K</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-1K</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-100</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-10K</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-50K</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-5k</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-4,7k</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>1N4148-T</t>
+  </si>
+  <si>
+    <t>Kingbright</t>
+  </si>
+  <si>
+    <t>WP7113ID</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>3386F-1-104LF</t>
+  </si>
+  <si>
+    <t>Neutrik</t>
+  </si>
+  <si>
+    <t>NJ2FD-V</t>
+  </si>
+  <si>
+    <t>Phoenix Contact</t>
+  </si>
+  <si>
+    <t>Terminal Block 3P 5.08mm</t>
+  </si>
+  <si>
+    <t>Edit color if needed</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>Potentiometer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +387,12 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -372,7 +447,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -435,6 +510,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -814,264 +890,284 @@
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>15</v>
-      </c>
       <c r="H7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1">
       <c r="A8" s="11">
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="11">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="11">
-        <v>10</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="H8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="14"/>
+      <c r="I8" s="14" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="7">
         <v>3</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="10"/>
+      <c r="I9" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="7">
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="7">
         <v>2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="7">
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="7">
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="10"/>
+      <c r="I12" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="7">
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7">
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7">
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="7">
         <v>7</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>33</v>
-      </c>
       <c r="H15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1">
       <c r="A16" s="11">
         <v>10</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="11">
         <v>1</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="14"/>
+      <c r="H16" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7">
@@ -1084,22 +1180,22 @@
         <v>1</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="15" t="s">
+      <c r="H17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1107,28 +1203,28 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>44</v>
-      </c>
       <c r="H18" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1136,55 +1232,57 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7">
         <v>4</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="10"/>
+      <c r="I19" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="7">
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="7">
         <v>2</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="F20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1192,27 +1290,29 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>13</v>
+        <v>71</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1757242</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="10"/>
+      <c r="I21" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="18"/>
@@ -1255,7 +1355,7 @@
     <mergeCell ref="A2:B3"/>
   </mergeCells>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
